--- a/toeic-test-v5/trial1-v2.xlsx
+++ b/toeic-test-v5/trial1-v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58984CC0-6067-49D0-8484-00ECB7868B96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF31B6E6-CE59-438E-983A-CFA9317C83FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1425" yWindow="1860" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7995" yWindow="975" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="19">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -119,6 +119,9 @@
     <t>D</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>C</t>
+  </si>
 </sst>
 </file>
 
@@ -160,10 +163,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -515,14 +517,14 @@
       </c>
       <c r="C6">
         <f>SUM(listening!C73:C102)</f>
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D6">
         <v>30</v>
       </c>
       <c r="E6" s="1">
         <f t="shared" si="0"/>
-        <v>0.36666666666666664</v>
+        <v>0.6333333333333333</v>
       </c>
     </row>
     <row r="8" spans="2:5">
@@ -577,14 +579,14 @@
       </c>
       <c r="C11">
         <f>SUM(reading!C55:C102)</f>
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D11">
         <v>48</v>
       </c>
       <c r="E11" s="1">
         <f t="shared" si="1"/>
-        <v>0.16666666666666666</v>
+        <v>0.3125</v>
       </c>
     </row>
   </sheetData>
@@ -601,863 +603,741 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="2">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
+      <c r="A3">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="2">
+      <c r="A4">
         <v>2</v>
       </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="2">
+      <c r="A5">
         <f>A4+1</f>
         <v>3</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="2">
+      <c r="A6">
         <f t="shared" ref="A6:A69" si="0">A5+1</f>
         <v>4</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="2">
+      <c r="A7">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="2">
+      <c r="A8">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="2">
+      <c r="A9">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="2">
+      <c r="A10">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="2">
+      <c r="A11">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="2">
+      <c r="A12">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="2">
+      <c r="A13">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="2">
+      <c r="A14">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="2">
+      <c r="A15">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="2">
+      <c r="A16">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="2">
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="2">
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="2">
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="2">
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="2">
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="2">
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="2">
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="2">
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="2">
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="2">
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="2">
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="2">
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="2">
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="2">
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="2">
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="2">
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="2">
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="2">
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="2">
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="2">
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="2">
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="B37" s="2"/>
-      <c r="C37" s="2"/>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="2">
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="2">
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="2">
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="B40" s="2"/>
-      <c r="C40" s="2"/>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="2">
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="B41" s="2"/>
-      <c r="C41" s="2"/>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="2">
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="B42" s="2"/>
-      <c r="C42" s="2"/>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="2">
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="B43" s="2"/>
-      <c r="C43" s="2"/>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="2">
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="2">
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="2">
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
-    </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="2">
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="B47" s="2"/>
-      <c r="C47" s="2"/>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="2">
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="2">
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="B49" s="2"/>
-      <c r="C49" s="2"/>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="2">
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="B50" s="2"/>
-      <c r="C50" s="2"/>
-    </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="2">
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
-      <c r="B51" s="2"/>
-      <c r="C51" s="2"/>
-    </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="2">
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="B52" s="2"/>
-      <c r="C52" s="2"/>
-    </row>
-    <row r="53" spans="1:3">
-      <c r="A53" s="2">
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
-      <c r="B53" s="2"/>
-      <c r="C53" s="2"/>
-    </row>
-    <row r="54" spans="1:3">
-      <c r="A54" s="2">
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="B54" s="2"/>
-      <c r="C54" s="2"/>
-    </row>
-    <row r="55" spans="1:3">
-      <c r="A55" s="2">
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
-      <c r="B55" s="2"/>
-      <c r="C55" s="2"/>
-    </row>
-    <row r="56" spans="1:3">
-      <c r="A56" s="2">
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="B56" s="2"/>
-      <c r="C56" s="2"/>
-    </row>
-    <row r="57" spans="1:3">
-      <c r="A57" s="2">
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
-      <c r="B57" s="2"/>
-      <c r="C57" s="2"/>
-    </row>
-    <row r="58" spans="1:3">
-      <c r="A58" s="2">
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
-      <c r="B58" s="2"/>
-      <c r="C58" s="2"/>
-    </row>
-    <row r="59" spans="1:3">
-      <c r="A59" s="2">
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59">
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
-      <c r="B59" s="2"/>
-      <c r="C59" s="2"/>
-    </row>
-    <row r="60" spans="1:3">
-      <c r="A60" s="2">
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
-      <c r="B60" s="2"/>
-      <c r="C60" s="2"/>
-    </row>
-    <row r="61" spans="1:3">
-      <c r="A61" s="2">
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61">
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
-      <c r="B61" s="2"/>
-      <c r="C61" s="2"/>
-    </row>
-    <row r="62" spans="1:3">
-      <c r="A62" s="2">
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="B62" s="2"/>
-      <c r="C62" s="2"/>
-    </row>
-    <row r="63" spans="1:3">
-      <c r="A63" s="2">
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
-      <c r="B63" s="2"/>
-      <c r="C63" s="2"/>
-    </row>
-    <row r="64" spans="1:3">
-      <c r="A64" s="2">
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64">
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
-      <c r="B64" s="2"/>
-      <c r="C64" s="2"/>
-    </row>
-    <row r="65" spans="1:3">
-      <c r="A65" s="2">
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65">
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
-      <c r="B65" s="2"/>
-      <c r="C65" s="2"/>
-    </row>
-    <row r="66" spans="1:3">
-      <c r="A66" s="2">
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
-      <c r="B66" s="2"/>
-      <c r="C66" s="2"/>
-    </row>
-    <row r="67" spans="1:3">
-      <c r="A67" s="2">
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67">
         <f t="shared" si="0"/>
         <v>65</v>
       </c>
-      <c r="B67" s="2"/>
-      <c r="C67" s="2"/>
-    </row>
-    <row r="68" spans="1:3">
-      <c r="A68" s="2">
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68">
         <f t="shared" si="0"/>
         <v>66</v>
       </c>
-      <c r="B68" s="2"/>
-      <c r="C68" s="2"/>
-    </row>
-    <row r="69" spans="1:3">
-      <c r="A69" s="2">
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69">
         <f t="shared" si="0"/>
         <v>67</v>
       </c>
-      <c r="B69" s="2"/>
-      <c r="C69" s="2"/>
-    </row>
-    <row r="70" spans="1:3">
-      <c r="A70" s="2">
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70">
         <f t="shared" ref="A70:A102" si="1">A69+1</f>
         <v>68</v>
       </c>
-      <c r="B70" s="2"/>
-      <c r="C70" s="2"/>
-    </row>
-    <row r="71" spans="1:3">
-      <c r="A71" s="2">
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71">
         <f t="shared" si="1"/>
         <v>69</v>
       </c>
-      <c r="B71" s="2"/>
-      <c r="C71" s="2"/>
-    </row>
-    <row r="72" spans="1:3">
-      <c r="A72" s="2">
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72">
         <f t="shared" si="1"/>
         <v>70</v>
       </c>
-      <c r="B72" s="2"/>
-      <c r="C72" s="2"/>
-    </row>
-    <row r="73" spans="1:3">
-      <c r="A73" s="2">
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73">
         <f t="shared" si="1"/>
         <v>71</v>
       </c>
-      <c r="B73" s="2"/>
-      <c r="C73" s="2"/>
-    </row>
-    <row r="74" spans="1:3">
-      <c r="A74" s="2">
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74">
         <f t="shared" si="1"/>
         <v>72</v>
       </c>
-      <c r="B74" s="2"/>
-      <c r="C74" s="2"/>
-    </row>
-    <row r="75" spans="1:3">
-      <c r="A75" s="2">
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75">
         <f t="shared" si="1"/>
         <v>73</v>
       </c>
-      <c r="B75" s="2"/>
-      <c r="C75" s="2"/>
-    </row>
-    <row r="76" spans="1:3">
-      <c r="A76" s="2">
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76">
         <f t="shared" si="1"/>
         <v>74</v>
       </c>
-      <c r="B76" s="2"/>
-      <c r="C76" s="2"/>
-    </row>
-    <row r="77" spans="1:3">
-      <c r="A77" s="2">
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77">
         <f t="shared" si="1"/>
         <v>75</v>
       </c>
-      <c r="B77" s="2"/>
-      <c r="C77" s="2"/>
-    </row>
-    <row r="78" spans="1:3">
-      <c r="A78" s="2">
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78">
         <f t="shared" si="1"/>
         <v>76</v>
       </c>
-      <c r="B78" s="2"/>
-      <c r="C78" s="2"/>
-    </row>
-    <row r="79" spans="1:3">
-      <c r="A79" s="2">
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79">
         <f t="shared" si="1"/>
         <v>77</v>
       </c>
-      <c r="B79" s="2"/>
-      <c r="C79" s="2"/>
-    </row>
-    <row r="80" spans="1:3">
-      <c r="A80" s="2">
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80">
         <f t="shared" si="1"/>
         <v>78</v>
       </c>
-      <c r="B80" s="2"/>
-      <c r="C80" s="2"/>
     </row>
     <row r="81" spans="1:3">
-      <c r="A81" s="2">
+      <c r="A81">
         <f t="shared" si="1"/>
         <v>79</v>
       </c>
-      <c r="B81" s="2"/>
-      <c r="C81" s="2"/>
     </row>
     <row r="82" spans="1:3">
-      <c r="A82" s="2">
+      <c r="A82">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="B82" s="2"/>
-      <c r="C82" s="2"/>
+      <c r="B82" t="s">
+        <v>12</v>
+      </c>
+      <c r="C82">
+        <v>1</v>
+      </c>
     </row>
     <row r="83" spans="1:3">
-      <c r="A83" s="2">
+      <c r="A83">
         <f t="shared" si="1"/>
         <v>81</v>
       </c>
-      <c r="B83" s="2"/>
-      <c r="C83" s="2"/>
+      <c r="B83" t="s">
+        <v>11</v>
+      </c>
+      <c r="C83">
+        <v>1</v>
+      </c>
     </row>
     <row r="84" spans="1:3">
-      <c r="A84" s="2">
+      <c r="A84">
         <f t="shared" si="1"/>
         <v>82</v>
       </c>
-      <c r="B84" s="2"/>
-      <c r="C84" s="2"/>
+      <c r="B84" t="s">
+        <v>18</v>
+      </c>
+      <c r="C84">
+        <v>1</v>
+      </c>
     </row>
     <row r="85" spans="1:3">
-      <c r="A85" s="2">
+      <c r="A85">
         <f t="shared" si="1"/>
         <v>83</v>
       </c>
-      <c r="B85" s="2"/>
-      <c r="C85" s="2"/>
+      <c r="B85" t="s">
+        <v>12</v>
+      </c>
+      <c r="C85">
+        <v>1</v>
+      </c>
     </row>
     <row r="86" spans="1:3">
-      <c r="A86" s="2">
+      <c r="A86">
         <f t="shared" si="1"/>
         <v>84</v>
       </c>
-      <c r="B86" s="2"/>
-      <c r="C86" s="2"/>
+      <c r="B86" t="s">
+        <v>13</v>
+      </c>
+      <c r="C86">
+        <v>1</v>
+      </c>
     </row>
     <row r="87" spans="1:3">
-      <c r="A87" s="2">
+      <c r="A87">
         <f t="shared" si="1"/>
         <v>85</v>
       </c>
-      <c r="B87" s="2"/>
-      <c r="C87" s="2"/>
+      <c r="B87" t="s">
+        <v>18</v>
+      </c>
+      <c r="C87">
+        <v>1</v>
+      </c>
     </row>
     <row r="88" spans="1:3">
-      <c r="A88" s="2">
+      <c r="A88">
         <f t="shared" si="1"/>
         <v>86</v>
       </c>
-      <c r="B88" s="2"/>
-      <c r="C88" s="2"/>
+      <c r="B88" t="s">
+        <v>13</v>
+      </c>
+      <c r="C88">
+        <v>1</v>
+      </c>
     </row>
     <row r="89" spans="1:3">
-      <c r="A89" s="2">
+      <c r="A89">
         <f t="shared" si="1"/>
         <v>87</v>
       </c>
-      <c r="B89" s="2"/>
-      <c r="C89" s="2"/>
+      <c r="B89" t="s">
+        <v>18</v>
+      </c>
+      <c r="C89">
+        <v>1</v>
+      </c>
     </row>
     <row r="90" spans="1:3">
-      <c r="A90" s="2">
+      <c r="A90">
         <f t="shared" si="1"/>
         <v>88</v>
       </c>
-      <c r="B90" s="2"/>
-      <c r="C90" s="2"/>
+      <c r="B90" t="s">
+        <v>18</v>
+      </c>
+      <c r="C90">
+        <v>0</v>
+      </c>
     </row>
     <row r="91" spans="1:3">
-      <c r="A91" s="2">
+      <c r="A91">
         <f t="shared" si="1"/>
         <v>89</v>
       </c>
-      <c r="B91" s="2" t="s">
+      <c r="B91" t="s">
         <v>14</v>
       </c>
-      <c r="C91" s="2">
+      <c r="C91">
         <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:3">
-      <c r="A92" s="2">
+      <c r="A92">
         <f t="shared" si="1"/>
         <v>90</v>
       </c>
-      <c r="B92" s="2" t="s">
+      <c r="B92" t="s">
         <v>14</v>
       </c>
-      <c r="C92" s="2">
+      <c r="C92">
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:3">
-      <c r="A93" s="2">
+      <c r="A93">
         <f t="shared" si="1"/>
         <v>91</v>
       </c>
-      <c r="B93" s="2" t="s">
+      <c r="B93" t="s">
         <v>15</v>
       </c>
-      <c r="C93" s="2">
+      <c r="C93">
         <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:3">
-      <c r="A94" s="2">
+      <c r="A94">
         <f t="shared" si="1"/>
         <v>92</v>
       </c>
-      <c r="B94" s="2" t="s">
+      <c r="B94" t="s">
         <v>13</v>
       </c>
-      <c r="C94" s="2">
+      <c r="C94">
         <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:3">
-      <c r="A95" s="2">
+      <c r="A95">
         <f t="shared" si="1"/>
         <v>93</v>
       </c>
-      <c r="B95" s="2" t="s">
+      <c r="B95" t="s">
         <v>11</v>
       </c>
-      <c r="C95" s="2">
+      <c r="C95">
         <v>1</v>
       </c>
     </row>
     <row r="96" spans="1:3">
-      <c r="A96" s="2">
+      <c r="A96">
         <f t="shared" si="1"/>
         <v>94</v>
       </c>
-      <c r="B96" s="2" t="s">
+      <c r="B96" t="s">
         <v>12</v>
       </c>
-      <c r="C96" s="2">
+      <c r="C96">
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="1:3">
-      <c r="A97" s="2">
+      <c r="A97">
         <f t="shared" si="1"/>
         <v>95</v>
       </c>
-      <c r="B97" s="2" t="s">
+      <c r="B97" t="s">
         <v>13</v>
       </c>
-      <c r="C97" s="2">
+      <c r="C97">
         <v>1</v>
       </c>
     </row>
     <row r="98" spans="1:3">
-      <c r="A98" s="2">
+      <c r="A98">
         <f t="shared" si="1"/>
         <v>96</v>
       </c>
-      <c r="B98" s="2" t="s">
+      <c r="B98" t="s">
         <v>16</v>
       </c>
-      <c r="C98" s="2">
+      <c r="C98">
         <v>1</v>
       </c>
     </row>
     <row r="99" spans="1:3">
-      <c r="A99" s="2">
+      <c r="A99">
         <f t="shared" si="1"/>
         <v>97</v>
       </c>
-      <c r="B99" s="2" t="s">
+      <c r="B99" t="s">
         <v>15</v>
       </c>
-      <c r="C99" s="2">
+      <c r="C99">
         <v>1</v>
       </c>
     </row>
     <row r="100" spans="1:3">
-      <c r="A100" s="2">
+      <c r="A100">
         <f t="shared" si="1"/>
         <v>98</v>
       </c>
-      <c r="B100" s="2" t="s">
+      <c r="B100" t="s">
         <v>11</v>
       </c>
-      <c r="C100" s="2">
+      <c r="C100">
         <v>1</v>
       </c>
     </row>
     <row r="101" spans="1:3">
-      <c r="A101" s="2">
+      <c r="A101">
         <f t="shared" si="1"/>
         <v>99</v>
       </c>
-      <c r="B101" s="2" t="s">
+      <c r="B101" t="s">
         <v>17</v>
       </c>
-      <c r="C101" s="2">
+      <c r="C101">
         <v>1</v>
       </c>
     </row>
     <row r="102" spans="1:3">
-      <c r="A102" s="2">
+      <c r="A102">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
-      <c r="B102" s="2" t="s">
+      <c r="B102" t="s">
         <v>16</v>
       </c>
-      <c r="C102" s="2">
+      <c r="C102">
         <v>1</v>
       </c>
     </row>
@@ -1481,7 +1361,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1496,841 +1376,721 @@
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="2">
+      <c r="A3">
         <v>101</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="2">
+      <c r="A4">
         <f>A3+1</f>
         <v>102</v>
       </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="2">
+      <c r="A5">
         <f t="shared" ref="A5:A68" si="0">A4+1</f>
         <v>103</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="2">
+      <c r="A6">
         <f t="shared" si="0"/>
         <v>104</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="2">
+      <c r="A7">
         <f t="shared" si="0"/>
         <v>105</v>
       </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="2">
+      <c r="A8">
         <f t="shared" si="0"/>
         <v>106</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="2">
+      <c r="A9">
         <f t="shared" si="0"/>
         <v>107</v>
       </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="2">
+      <c r="A10">
         <f t="shared" si="0"/>
         <v>108</v>
       </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="2">
+      <c r="A11">
         <f t="shared" si="0"/>
         <v>109</v>
       </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="2">
+      <c r="A12">
         <f t="shared" si="0"/>
         <v>110</v>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="2">
+      <c r="A13">
         <f t="shared" si="0"/>
         <v>111</v>
       </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="2">
+      <c r="A14">
         <f t="shared" si="0"/>
         <v>112</v>
       </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="2">
+      <c r="A15">
         <f t="shared" si="0"/>
         <v>113</v>
       </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="2">
+      <c r="A16">
         <f t="shared" si="0"/>
         <v>114</v>
       </c>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="2">
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17">
         <f t="shared" si="0"/>
         <v>115</v>
       </c>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="2">
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18">
         <f t="shared" si="0"/>
         <v>116</v>
       </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="2">
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19">
         <f t="shared" si="0"/>
         <v>117</v>
       </c>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="2">
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20">
         <f t="shared" si="0"/>
         <v>118</v>
       </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="2">
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21">
         <f t="shared" si="0"/>
         <v>119</v>
       </c>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="2">
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22">
         <f t="shared" si="0"/>
         <v>120</v>
       </c>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="2">
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23">
         <f t="shared" si="0"/>
         <v>121</v>
       </c>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="2">
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24">
         <f t="shared" si="0"/>
         <v>122</v>
       </c>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="2">
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25">
         <f t="shared" si="0"/>
         <v>123</v>
       </c>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="2">
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26">
         <f t="shared" si="0"/>
         <v>124</v>
       </c>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="2">
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27">
         <f t="shared" si="0"/>
         <v>125</v>
       </c>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="2">
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28">
         <f t="shared" si="0"/>
         <v>126</v>
       </c>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="2">
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29">
         <f t="shared" si="0"/>
         <v>127</v>
       </c>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="2">
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30">
         <f t="shared" si="0"/>
         <v>128</v>
       </c>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="2">
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31">
         <f t="shared" si="0"/>
         <v>129</v>
       </c>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="2">
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32">
         <f t="shared" si="0"/>
         <v>130</v>
       </c>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="2">
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33">
         <f t="shared" si="0"/>
         <v>131</v>
       </c>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="2">
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34">
         <f t="shared" si="0"/>
         <v>132</v>
       </c>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="2">
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35">
         <f t="shared" si="0"/>
         <v>133</v>
       </c>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="2">
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36">
         <f t="shared" si="0"/>
         <v>134</v>
       </c>
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="2">
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37">
         <f t="shared" si="0"/>
         <v>135</v>
       </c>
-      <c r="B37" s="2"/>
-      <c r="C37" s="2"/>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="2">
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38">
         <f t="shared" si="0"/>
         <v>136</v>
       </c>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="2">
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39">
         <f t="shared" si="0"/>
         <v>137</v>
       </c>
-      <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="2">
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40">
         <f t="shared" si="0"/>
         <v>138</v>
       </c>
-      <c r="B40" s="2"/>
-      <c r="C40" s="2"/>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="2">
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41">
         <f t="shared" si="0"/>
         <v>139</v>
       </c>
-      <c r="B41" s="2"/>
-      <c r="C41" s="2"/>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="2">
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42">
         <f t="shared" si="0"/>
         <v>140</v>
       </c>
-      <c r="B42" s="2"/>
-      <c r="C42" s="2"/>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="2">
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43">
         <f t="shared" si="0"/>
         <v>141</v>
       </c>
-      <c r="B43" s="2"/>
-      <c r="C43" s="2"/>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="2">
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44">
         <f t="shared" si="0"/>
         <v>142</v>
       </c>
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="2">
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45">
         <f t="shared" si="0"/>
         <v>143</v>
       </c>
-      <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="2">
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46">
         <f t="shared" si="0"/>
         <v>144</v>
       </c>
-      <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
-    </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="2">
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47">
         <f t="shared" si="0"/>
         <v>145</v>
       </c>
-      <c r="B47" s="2"/>
-      <c r="C47" s="2"/>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="2">
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48">
         <f t="shared" si="0"/>
         <v>146</v>
       </c>
-      <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="2">
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49">
         <f t="shared" si="0"/>
         <v>147</v>
       </c>
-      <c r="B49" s="2"/>
-      <c r="C49" s="2"/>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="2">
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50">
         <f t="shared" si="0"/>
         <v>148</v>
       </c>
-      <c r="B50" s="2"/>
-      <c r="C50" s="2"/>
-    </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="2">
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51">
         <f t="shared" si="0"/>
         <v>149</v>
       </c>
-      <c r="B51" s="2"/>
-      <c r="C51" s="2"/>
-    </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="2">
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52">
         <f t="shared" si="0"/>
         <v>150</v>
       </c>
-      <c r="B52" s="2"/>
-      <c r="C52" s="2"/>
-    </row>
-    <row r="53" spans="1:3">
-      <c r="A53" s="2">
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53">
         <f t="shared" si="0"/>
         <v>151</v>
       </c>
-      <c r="B53" s="2"/>
-      <c r="C53" s="2"/>
-    </row>
-    <row r="54" spans="1:3">
-      <c r="A54" s="2">
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54">
         <f t="shared" si="0"/>
         <v>152</v>
       </c>
-      <c r="B54" s="2"/>
-      <c r="C54" s="2"/>
-    </row>
-    <row r="55" spans="1:3">
-      <c r="A55" s="2">
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55">
         <f t="shared" si="0"/>
         <v>153</v>
       </c>
-      <c r="B55" s="2"/>
-      <c r="C55" s="2"/>
-    </row>
-    <row r="56" spans="1:3">
-      <c r="A56" s="2">
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56">
         <f t="shared" si="0"/>
         <v>154</v>
       </c>
-      <c r="B56" s="2"/>
-      <c r="C56" s="2"/>
-    </row>
-    <row r="57" spans="1:3">
-      <c r="A57" s="2">
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57">
         <f t="shared" si="0"/>
         <v>155</v>
       </c>
-      <c r="B57" s="2"/>
-      <c r="C57" s="2"/>
-    </row>
-    <row r="58" spans="1:3">
-      <c r="A58" s="2">
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58">
         <f t="shared" si="0"/>
         <v>156</v>
       </c>
-      <c r="B58" s="2"/>
-      <c r="C58" s="2"/>
-    </row>
-    <row r="59" spans="1:3">
-      <c r="A59" s="2">
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59">
         <f t="shared" si="0"/>
         <v>157</v>
       </c>
-      <c r="B59" s="2"/>
-      <c r="C59" s="2"/>
-    </row>
-    <row r="60" spans="1:3">
-      <c r="A60" s="2">
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60">
         <f t="shared" si="0"/>
         <v>158</v>
       </c>
-      <c r="B60" s="2"/>
-      <c r="C60" s="2"/>
-    </row>
-    <row r="61" spans="1:3">
-      <c r="A61" s="2">
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61">
         <f t="shared" si="0"/>
         <v>159</v>
       </c>
-      <c r="B61" s="2"/>
-      <c r="C61" s="2"/>
-    </row>
-    <row r="62" spans="1:3">
-      <c r="A62" s="2">
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62">
         <f t="shared" si="0"/>
         <v>160</v>
       </c>
-      <c r="B62" s="2"/>
-      <c r="C62" s="2"/>
-    </row>
-    <row r="63" spans="1:3">
-      <c r="A63" s="2">
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63">
         <f t="shared" si="0"/>
         <v>161</v>
       </c>
-      <c r="B63" s="2"/>
-      <c r="C63" s="2"/>
-    </row>
-    <row r="64" spans="1:3">
-      <c r="A64" s="2">
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64">
         <f t="shared" si="0"/>
         <v>162</v>
       </c>
-      <c r="B64" s="2"/>
-      <c r="C64" s="2"/>
-    </row>
-    <row r="65" spans="1:3">
-      <c r="A65" s="2">
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65">
         <f t="shared" si="0"/>
         <v>163</v>
       </c>
-      <c r="B65" s="2"/>
-      <c r="C65" s="2"/>
-    </row>
-    <row r="66" spans="1:3">
-      <c r="A66" s="2">
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66">
         <f t="shared" si="0"/>
         <v>164</v>
       </c>
-      <c r="B66" s="2"/>
-      <c r="C66" s="2"/>
-    </row>
-    <row r="67" spans="1:3">
-      <c r="A67" s="2">
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67">
         <f t="shared" si="0"/>
         <v>165</v>
       </c>
-      <c r="B67" s="2"/>
-      <c r="C67" s="2"/>
-    </row>
-    <row r="68" spans="1:3">
-      <c r="A68" s="2">
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68">
         <f t="shared" si="0"/>
         <v>166</v>
       </c>
-      <c r="B68" s="2"/>
-      <c r="C68" s="2"/>
-    </row>
-    <row r="69" spans="1:3">
-      <c r="A69" s="2">
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69">
         <f t="shared" ref="A69:A102" si="1">A68+1</f>
         <v>167</v>
       </c>
-      <c r="B69" s="2"/>
-      <c r="C69" s="2"/>
-    </row>
-    <row r="70" spans="1:3">
-      <c r="A70" s="2">
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70">
         <f t="shared" si="1"/>
         <v>168</v>
       </c>
-      <c r="B70" s="2"/>
-      <c r="C70" s="2"/>
-    </row>
-    <row r="71" spans="1:3">
-      <c r="A71" s="2">
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71">
         <f t="shared" si="1"/>
         <v>169</v>
       </c>
-      <c r="B71" s="2"/>
-      <c r="C71" s="2"/>
-    </row>
-    <row r="72" spans="1:3">
-      <c r="A72" s="2">
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72">
         <f t="shared" si="1"/>
         <v>170</v>
       </c>
-      <c r="B72" s="2"/>
-      <c r="C72" s="2"/>
-    </row>
-    <row r="73" spans="1:3">
-      <c r="A73" s="2">
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73">
         <f t="shared" si="1"/>
         <v>171</v>
       </c>
-      <c r="B73" s="2"/>
-      <c r="C73" s="2"/>
-    </row>
-    <row r="74" spans="1:3">
-      <c r="A74" s="2">
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74">
         <f t="shared" si="1"/>
         <v>172</v>
       </c>
-      <c r="B74" s="2"/>
-      <c r="C74" s="2"/>
-    </row>
-    <row r="75" spans="1:3">
-      <c r="A75" s="2">
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75">
         <f t="shared" si="1"/>
         <v>173</v>
       </c>
-      <c r="B75" s="2"/>
-      <c r="C75" s="2"/>
-    </row>
-    <row r="76" spans="1:3">
-      <c r="A76" s="2">
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76">
         <f t="shared" si="1"/>
         <v>174</v>
       </c>
-      <c r="B76" s="2"/>
-      <c r="C76" s="2"/>
-    </row>
-    <row r="77" spans="1:3">
-      <c r="A77" s="2">
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77">
         <f t="shared" si="1"/>
         <v>175</v>
       </c>
-      <c r="B77" s="2"/>
-      <c r="C77" s="2"/>
-    </row>
-    <row r="78" spans="1:3">
-      <c r="A78" s="2">
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78">
         <f t="shared" si="1"/>
         <v>176</v>
       </c>
-      <c r="B78" s="2"/>
-      <c r="C78" s="2"/>
-    </row>
-    <row r="79" spans="1:3">
-      <c r="A79" s="2">
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79">
         <f t="shared" si="1"/>
         <v>177</v>
       </c>
-      <c r="B79" s="2"/>
-      <c r="C79" s="2"/>
-    </row>
-    <row r="80" spans="1:3">
-      <c r="A80" s="2">
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80">
         <f t="shared" si="1"/>
         <v>178</v>
       </c>
-      <c r="B80" s="2"/>
-      <c r="C80" s="2"/>
     </row>
     <row r="81" spans="1:3">
-      <c r="A81" s="2">
+      <c r="A81">
         <f t="shared" si="1"/>
         <v>179</v>
       </c>
-      <c r="B81" s="2"/>
-      <c r="C81" s="2"/>
     </row>
     <row r="82" spans="1:3">
-      <c r="A82" s="2">
+      <c r="A82">
         <f t="shared" si="1"/>
         <v>180</v>
       </c>
-      <c r="B82" s="2"/>
-      <c r="C82" s="2"/>
     </row>
     <row r="83" spans="1:3">
-      <c r="A83" s="2">
+      <c r="A83">
         <f t="shared" si="1"/>
         <v>181</v>
       </c>
-      <c r="B83" s="2"/>
-      <c r="C83" s="2"/>
+      <c r="B83" t="s">
+        <v>9</v>
+      </c>
+      <c r="C83">
+        <v>1</v>
+      </c>
     </row>
     <row r="84" spans="1:3">
-      <c r="A84" s="2">
+      <c r="A84">
         <f t="shared" si="1"/>
         <v>182</v>
       </c>
-      <c r="B84" s="2"/>
-      <c r="C84" s="2"/>
+      <c r="B84" t="s">
+        <v>10</v>
+      </c>
+      <c r="C84">
+        <v>1</v>
+      </c>
     </row>
     <row r="85" spans="1:3">
-      <c r="A85" s="2">
+      <c r="A85">
         <f t="shared" si="1"/>
         <v>183</v>
       </c>
-      <c r="B85" s="2"/>
-      <c r="C85" s="2"/>
+      <c r="B85" t="s">
+        <v>8</v>
+      </c>
+      <c r="C85">
+        <v>1</v>
+      </c>
     </row>
     <row r="86" spans="1:3">
-      <c r="A86" s="2">
+      <c r="A86">
         <f t="shared" si="1"/>
         <v>184</v>
       </c>
-      <c r="B86" s="2"/>
-      <c r="C86" s="2"/>
+      <c r="B86" t="s">
+        <v>10</v>
+      </c>
+      <c r="C86">
+        <v>0</v>
+      </c>
     </row>
     <row r="87" spans="1:3">
-      <c r="A87" s="2">
+      <c r="A87">
         <f t="shared" si="1"/>
         <v>185</v>
       </c>
-      <c r="B87" s="2"/>
-      <c r="C87" s="2"/>
+      <c r="B87" t="s">
+        <v>8</v>
+      </c>
+      <c r="C87">
+        <v>1</v>
+      </c>
     </row>
     <row r="88" spans="1:3">
-      <c r="A88" s="2">
+      <c r="A88">
         <f t="shared" si="1"/>
         <v>186</v>
       </c>
-      <c r="B88" s="2"/>
-      <c r="C88" s="2"/>
+      <c r="B88" t="s">
+        <v>9</v>
+      </c>
+      <c r="C88">
+        <v>0</v>
+      </c>
     </row>
     <row r="89" spans="1:3">
-      <c r="A89" s="2">
+      <c r="A89">
         <f t="shared" si="1"/>
         <v>187</v>
       </c>
-      <c r="B89" s="2"/>
-      <c r="C89" s="2"/>
+      <c r="B89" t="s">
+        <v>10</v>
+      </c>
+      <c r="C89">
+        <v>1</v>
+      </c>
     </row>
     <row r="90" spans="1:3">
-      <c r="A90" s="2">
+      <c r="A90">
         <f t="shared" si="1"/>
         <v>188</v>
       </c>
-      <c r="B90" s="2"/>
-      <c r="C90" s="2"/>
+      <c r="B90" t="s">
+        <v>10</v>
+      </c>
+      <c r="C90">
+        <v>0</v>
+      </c>
     </row>
     <row r="91" spans="1:3">
-      <c r="A91" s="2">
+      <c r="A91">
         <f t="shared" si="1"/>
         <v>189</v>
       </c>
-      <c r="B91" s="2"/>
-      <c r="C91" s="2"/>
+      <c r="B91" t="s">
+        <v>10</v>
+      </c>
+      <c r="C91">
+        <v>1</v>
+      </c>
     </row>
     <row r="92" spans="1:3">
-      <c r="A92" s="2">
+      <c r="A92">
         <f t="shared" si="1"/>
         <v>190</v>
       </c>
-      <c r="B92" s="2"/>
-      <c r="C92" s="2"/>
+      <c r="B92" t="s">
+        <v>7</v>
+      </c>
+      <c r="C92">
+        <v>1</v>
+      </c>
     </row>
     <row r="93" spans="1:3">
-      <c r="A93" s="2">
+      <c r="A93">
         <f t="shared" si="1"/>
         <v>191</v>
       </c>
-      <c r="B93" s="2" t="s">
+      <c r="B93" t="s">
         <v>10</v>
       </c>
-      <c r="C93" s="2">
+      <c r="C93">
         <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:3">
-      <c r="A94" s="2">
+      <c r="A94">
         <f t="shared" si="1"/>
         <v>192</v>
       </c>
-      <c r="B94" s="2" t="s">
+      <c r="B94" t="s">
         <v>9</v>
       </c>
-      <c r="C94" s="2">
+      <c r="C94">
         <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:3">
-      <c r="A95" s="2">
+      <c r="A95">
         <f t="shared" si="1"/>
         <v>193</v>
       </c>
-      <c r="B95" s="2" t="s">
+      <c r="B95" t="s">
         <v>8</v>
       </c>
-      <c r="C95" s="2">
+      <c r="C95">
         <v>1</v>
       </c>
     </row>
     <row r="96" spans="1:3">
-      <c r="A96" s="2">
+      <c r="A96">
         <f t="shared" si="1"/>
         <v>194</v>
       </c>
-      <c r="B96" s="2" t="s">
+      <c r="B96" t="s">
         <v>7</v>
       </c>
-      <c r="C96" s="2">
+      <c r="C96">
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="1:3">
-      <c r="A97" s="2">
+      <c r="A97">
         <f t="shared" si="1"/>
         <v>195</v>
       </c>
-      <c r="B97" s="2" t="s">
+      <c r="B97" t="s">
         <v>9</v>
       </c>
-      <c r="C97" s="2">
+      <c r="C97">
         <v>1</v>
       </c>
     </row>
     <row r="98" spans="1:3">
-      <c r="A98" s="2">
+      <c r="A98">
         <f t="shared" si="1"/>
         <v>196</v>
       </c>
-      <c r="B98" s="2" t="s">
+      <c r="B98" t="s">
         <v>7</v>
       </c>
-      <c r="C98" s="2">
+      <c r="C98">
         <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:3">
-      <c r="A99" s="2">
+      <c r="A99">
         <f t="shared" si="1"/>
         <v>197</v>
       </c>
-      <c r="B99" s="2" t="s">
+      <c r="B99" t="s">
         <v>9</v>
       </c>
-      <c r="C99" s="2">
+      <c r="C99">
         <v>1</v>
       </c>
     </row>
     <row r="100" spans="1:3">
-      <c r="A100" s="2">
+      <c r="A100">
         <f t="shared" si="1"/>
         <v>198</v>
       </c>
-      <c r="B100" s="2" t="s">
+      <c r="B100" t="s">
         <v>9</v>
       </c>
-      <c r="C100" s="2">
+      <c r="C100">
         <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:3">
-      <c r="A101" s="2">
+      <c r="A101">
         <f t="shared" si="1"/>
         <v>199</v>
       </c>
-      <c r="B101" s="2" t="s">
+      <c r="B101" t="s">
         <v>8</v>
       </c>
-      <c r="C101" s="2">
+      <c r="C101">
         <v>1</v>
       </c>
     </row>
     <row r="102" spans="1:3">
-      <c r="A102" s="2">
+      <c r="A102">
         <f t="shared" si="1"/>
         <v>200</v>
       </c>
-      <c r="B102" s="2" t="s">
+      <c r="B102" t="s">
         <v>7</v>
       </c>
-      <c r="C102" s="2">
+      <c r="C102">
         <v>1</v>
       </c>
     </row>

--- a/toeic-test-v5/trial1-v2.xlsx
+++ b/toeic-test-v5/trial1-v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF31B6E6-CE59-438E-983A-CFA9317C83FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F8D6D0A-D3DA-4950-BE46-8FBA6AFF94E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7995" yWindow="975" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8475" yWindow="1050" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="21">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -121,6 +121,14 @@
   </si>
   <si>
     <t>C</t>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -469,14 +477,14 @@
       </c>
       <c r="C3">
         <f>SUM(listening!C3:C12)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D3">
         <v>10</v>
       </c>
       <c r="E3" s="1">
         <f>C3/D3</f>
-        <v>0</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="4" spans="2:5">
@@ -547,14 +555,14 @@
       </c>
       <c r="C9">
         <f>SUM(reading!C3:C42)</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D9">
         <v>40</v>
       </c>
       <c r="E9" s="1">
         <f t="shared" ref="E9:E11" si="1">C9/D9</f>
-        <v>0</v>
+        <v>0.22500000000000001</v>
       </c>
     </row>
     <row r="10" spans="2:5">
@@ -603,7 +611,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -621,10 +629,22 @@
       <c r="A3">
         <v>1</v>
       </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
         <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -632,47 +652,95 @@
         <f>A4+1</f>
         <v>3</v>
       </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
         <f t="shared" ref="A6:A69" si="0">A5+1</f>
         <v>4</v>
       </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
+      <c r="B11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1361,7 +1429,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1378,6 +1446,12 @@
     <row r="3" spans="1:3">
       <c r="A3">
         <v>101</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1385,53 +1459,107 @@
         <f>A3+1</f>
         <v>102</v>
       </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
         <f t="shared" ref="A5:A68" si="0">A4+1</f>
         <v>103</v>
       </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>104</v>
       </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>105</v>
       </c>
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>106</v>
       </c>
+      <c r="B8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>107</v>
       </c>
+      <c r="B9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>108</v>
       </c>
+      <c r="B10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>109</v>
       </c>
+      <c r="B11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>110</v>
+      </c>
+      <c r="B12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:3">
